--- a/Compititor's_Price/IKO_Prices/IKO_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_24-09-2025.xlsx
@@ -503,12 +503,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.03</t>
+          <t>£10.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.03</t>
+          <t>£10.97</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.92</t>
+          <t>£12.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.92</t>
+          <t>£12.59</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.28</t>
+          <t>£16.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.28</t>
+          <t>£16.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.38</t>
+          <t>£16.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.38</t>
+          <t>£16.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.26</t>
+          <t>£20.79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.26</t>
+          <t>£20.79</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.63</t>
+          <t>£22.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.63</t>
+          <t>£22.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£23.12</t>
+          <t>£23.10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.12</t>
+          <t>£23.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£27.04</t>
+          <t>£26.46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£27.04</t>
+          <t>£26.46</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.40</t>
+          <t>£28.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.40</t>
+          <t>£28.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.22</t>
+          <t>£28.19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.22</t>
+          <t>£28.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£37.80</t>
+          <t>£37.33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£36.23</t>
+          <t>£34.60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£36.23</t>
+          <t>£34.60</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£42.97</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£42.97</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
